--- a/data/trans_orig/P1002-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>28360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47971</t>
+          <t>48840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447361</t>
+          <t>447467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464102</t>
+          <t>463600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279595</t>
+          <t>278320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295544</t>
+          <t>294725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732486</t>
+          <t>731617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755491</t>
+          <t>755785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>36852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28285</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53311</t>
+          <t>52088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>343671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359528</t>
+          <t>359497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334283</t>
+          <t>335013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354950</t>
+          <t>354589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685488</t>
+          <t>686711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710514</t>
+          <t>710523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39819</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59687</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502570</t>
+          <t>502499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523813</t>
+          <t>523201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141686</t>
+          <t>140583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158212</t>
+          <t>157562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650484</t>
+          <t>651530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>677307</t>
+          <t>677322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66240</t>
+          <t>66130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100450</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47702</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>77775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122846</t>
+          <t>121390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167770</t>
+          <t>167084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1137884</t>
+          <t>1138143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1172094</t>
+          <t>1172204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637398</t>
+          <t>636510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666583</t>
+          <t>667113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1784850</t>
+          <t>1785536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1829774</t>
+          <t>1831230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38247</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66182</t>
+          <t>65716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55806</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90311</t>
+          <t>89708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319394</t>
+          <t>319940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338193</t>
+          <t>338520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>502570</t>
+          <t>503036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>530505</t>
+          <t>531001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>828996</t>
+          <t>829599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>863501</t>
+          <t>863044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93833</t>
+          <t>91316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>136458</t>
+          <t>132418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102602</t>
+          <t>100801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147600</t>
+          <t>143491</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280644</t>
+          <t>280147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293317</t>
+          <t>293363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1112302</t>
+          <t>1116342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1154927</t>
+          <t>1157444</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1399360</t>
+          <t>1403469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1444358</t>
+          <t>1446159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145613</t>
+          <t>145695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197516</t>
+          <t>196437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>253226</t>
+          <t>256750</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320299</t>
+          <t>320399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418258</t>
+          <t>418523</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>498124</t>
+          <t>496873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3072674</t>
+          <t>3073753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3124577</t>
+          <t>3124495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3057825</t>
+          <t>3057725</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3124898</t>
+          <t>3121374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6150190</t>
+          <t>6151441</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6230056</t>
+          <t>6229791</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27719</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>53466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407930</t>
+          <t>409120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426414</t>
+          <t>427062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281967</t>
+          <t>280860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300443</t>
+          <t>300700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>695390</t>
+          <t>697262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>723009</t>
+          <t>723541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>35353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45726</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38086</t>
+          <t>40034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385973</t>
+          <t>383444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>406102</t>
+          <t>405332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>292285</t>
+          <t>291855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316689</t>
+          <t>316069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687907</t>
+          <t>687646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718722</t>
+          <t>716774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38917</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71740</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>58048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80269</t>
+          <t>79247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119780</t>
+          <t>118861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>557675</t>
+          <t>559419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590498</t>
+          <t>591292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202652</t>
+          <t>202081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227637</t>
+          <t>227152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>769764</t>
+          <t>770683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>809275</t>
+          <t>810297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>78499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117996</t>
+          <t>118536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74050</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111949</t>
+          <t>109061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161593</t>
+          <t>161303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217410</t>
+          <t>215704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1041013</t>
+          <t>1040473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1079905</t>
+          <t>1080510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654708</t>
+          <t>657596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692607</t>
+          <t>693039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1708257</t>
+          <t>1709963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1764074</t>
+          <t>1764364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42294</t>
+          <t>42090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123522</t>
+          <t>122322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167569</t>
+          <t>167724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>151319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200362</t>
+          <t>201429</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467248</t>
+          <t>467452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489650</t>
+          <t>489266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>591953</t>
+          <t>591798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>636000</t>
+          <t>637200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1068702</t>
+          <t>1067635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1121332</t>
+          <t>1117745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>139927</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186530</t>
+          <t>185924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151017</t>
+          <t>149032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201848</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246868</t>
+          <t>246155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260492</t>
+          <t>260891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>922821</t>
+          <t>923427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>969367</t>
+          <t>969424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1174385</t>
+          <t>1178493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1225216</t>
+          <t>1227201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197507</t>
+          <t>198273</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>258101</t>
+          <t>262471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>451249</t>
+          <t>456096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>537140</t>
+          <t>541365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>672406</t>
+          <t>672140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>774556</t>
+          <t>776028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3161818</t>
+          <t>3157448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3222412</t>
+          <t>3221646</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3010985</t>
+          <t>3006760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3096876</t>
+          <t>3092029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6193488</t>
+          <t>6192016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6295638</t>
+          <t>6295904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26589</t>
+          <t>26142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401697</t>
+          <t>402136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419572</t>
+          <t>420182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>316522</t>
+          <t>316849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334306</t>
+          <t>334574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>726847</t>
+          <t>725339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749558</t>
+          <t>750005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30238</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352736</t>
+          <t>352888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368669</t>
+          <t>368537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342035</t>
+          <t>341410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361190</t>
+          <t>360554</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702164</t>
+          <t>698924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725947</t>
+          <t>725508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45390</t>
+          <t>44122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71527</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476524</t>
+          <t>477792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499816</t>
+          <t>500045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131830</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151203</t>
+          <t>150961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616509</t>
+          <t>616470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645591</t>
+          <t>646377</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48144</t>
+          <t>47421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79407</t>
+          <t>79113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66998</t>
+          <t>67661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102723</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122217</t>
+          <t>123866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169548</t>
+          <t>167204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1070231</t>
+          <t>1070525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1101494</t>
+          <t>1102217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>723153</t>
+          <t>724481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758878</t>
+          <t>758215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805966</t>
+          <t>1808310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1853297</t>
+          <t>1851648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58560</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89911</t>
+          <t>90847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129136</t>
+          <t>132097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132036</t>
+          <t>132643</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181659</t>
+          <t>182469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>562146</t>
+          <t>559751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>587491</t>
+          <t>586310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>609108</t>
+          <t>606147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>648333</t>
+          <t>647397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1177291</t>
+          <t>1176481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1226914</t>
+          <t>1226307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100792</t>
+          <t>100835</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144475</t>
+          <t>145391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110976</t>
+          <t>110454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155869</t>
+          <t>155658</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267634</t>
+          <t>268041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281718</t>
+          <t>281690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>937550</t>
+          <t>936634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>981233</t>
+          <t>981190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1213301</t>
+          <t>1213512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1258194</t>
+          <t>1258716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>156808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210043</t>
+          <t>212982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>339962</t>
+          <t>343723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>418676</t>
+          <t>419177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>512978</t>
+          <t>512483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>604709</t>
+          <t>612765</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3175679</t>
+          <t>3172740</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3229653</t>
+          <t>3228914</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3112920</t>
+          <t>3112419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3191634</t>
+          <t>3187873</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6312609</t>
+          <t>6304553</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6404340</t>
+          <t>6404835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>36076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42741</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44549</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71842</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469645</t>
+          <t>469136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489137</t>
+          <t>489789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404726</t>
+          <t>405294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424119</t>
+          <t>425181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880837</t>
+          <t>882734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>908130</t>
+          <t>910817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41945</t>
+          <t>41921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>56285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>431253</t>
+          <t>432781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446075</t>
+          <t>446061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340635</t>
+          <t>340659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359845</t>
+          <t>361269</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778834</t>
+          <t>778508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803157</t>
+          <t>803577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>64029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79403</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>606074</t>
+          <t>604235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656468</t>
+          <t>655804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144534</t>
+          <t>144882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155843</t>
+          <t>156177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>755772</t>
+          <t>755682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814149</t>
+          <t>813461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51693</t>
+          <t>51043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82007</t>
+          <t>80929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150760</t>
+          <t>149285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>951605</t>
+          <t>952683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981919</t>
+          <t>982569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>895115</t>
+          <t>894075</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944025</t>
+          <t>946007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1860624</t>
+          <t>1862099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1921604</t>
+          <t>1921755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75952</t>
+          <t>79818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128201</t>
+          <t>129764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115943</t>
+          <t>116914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169594</t>
+          <t>168211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425802</t>
+          <t>426102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447993</t>
+          <t>447971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712575</t>
+          <t>711012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>764824</t>
+          <t>760958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1146227</t>
+          <t>1147610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1199878</t>
+          <t>1198907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123731</t>
+          <t>124231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99869</t>
+          <t>98567</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137566</t>
+          <t>137980</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215200</t>
+          <t>215742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236175</t>
+          <t>235767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>636692</t>
+          <t>636192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>669331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>863364</t>
+          <t>862950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>901061</t>
+          <t>902363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144413</t>
+          <t>138822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>216788</t>
+          <t>213214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>284887</t>
+          <t>292594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394394</t>
+          <t>392823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461284</t>
+          <t>461699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>593362</t>
+          <t>592714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3158066</t>
+          <t>3161640</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3230441</t>
+          <t>3236032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3181534</t>
+          <t>3183105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3291041</t>
+          <t>3283334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6357420</t>
+          <t>6358068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6489498</t>
+          <t>6489083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P1002-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28360</t>
+          <t>28084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>47774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>446806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>463600</t>
+          <t>463666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278320</t>
+          <t>278596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294725</t>
+          <t>295241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731617</t>
+          <t>732683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>755785</t>
+          <t>755754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36852</t>
+          <t>37848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>55043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343671</t>
+          <t>343843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359497</t>
+          <t>360164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335013</t>
+          <t>334017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354589</t>
+          <t>354530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686711</t>
+          <t>683756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710523</t>
+          <t>710665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58641</t>
+          <t>60801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502499</t>
+          <t>503526</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523201</t>
+          <t>523580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140583</t>
+          <t>141072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157562</t>
+          <t>157928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651530</t>
+          <t>649370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>677322</t>
+          <t>676854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66130</t>
+          <t>65032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>99225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>77526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121390</t>
+          <t>119615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167084</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138143</t>
+          <t>1139109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1172204</t>
+          <t>1173302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636510</t>
+          <t>636759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>667113</t>
+          <t>666568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1785536</t>
+          <t>1785523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1831230</t>
+          <t>1833005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>31608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>65475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56263</t>
+          <t>54951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89708</t>
+          <t>90103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319940</t>
+          <t>318947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338520</t>
+          <t>337713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>503036</t>
+          <t>503277</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>531001</t>
+          <t>529471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>829599</t>
+          <t>829204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>863044</t>
+          <t>864356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91316</t>
+          <t>91888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>132095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100801</t>
+          <t>101815</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143491</t>
+          <t>145183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280147</t>
+          <t>280846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293363</t>
+          <t>293549</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1116342</t>
+          <t>1116665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1157444</t>
+          <t>1156872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1403469</t>
+          <t>1401777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1446159</t>
+          <t>1445145</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145695</t>
+          <t>145474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196437</t>
+          <t>196815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>256750</t>
+          <t>251166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320399</t>
+          <t>318978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>456270</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>416556</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>505144</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>7,6%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>456270</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>418523</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>496873</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3073753</t>
+          <t>3073375</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3124495</t>
+          <t>3124716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3057725</t>
+          <t>3059146</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3121374</t>
+          <t>3126958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2954,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6059</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6192044</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6143170</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6231758</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>92,4%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6059</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6192044</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6151441</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6229791</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27154</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>33628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53466</t>
+          <t>53848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409120</t>
+          <t>408135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427062</t>
+          <t>426415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280860</t>
+          <t>280826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300700</t>
+          <t>300104</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697262</t>
+          <t>696880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>723541</t>
+          <t>723315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35353</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>44657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69162</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383444</t>
+          <t>387388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405332</t>
+          <t>406349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291855</t>
+          <t>293354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316069</t>
+          <t>315983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687646</t>
+          <t>684452</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716774</t>
+          <t>716720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>68129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58048</t>
+          <t>57783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79247</t>
+          <t>78203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118861</t>
+          <t>118481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>559419</t>
+          <t>561286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>591292</t>
+          <t>591757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202081</t>
+          <t>202346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227152</t>
+          <t>227838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>770683</t>
+          <t>771063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810297</t>
+          <t>811341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78499</t>
+          <t>78367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118536</t>
+          <t>116707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>73112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>109888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161303</t>
+          <t>160727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215704</t>
+          <t>216073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1040473</t>
+          <t>1042302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1080510</t>
+          <t>1080642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657596</t>
+          <t>656769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693039</t>
+          <t>693545</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1709963</t>
+          <t>1709594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1764364</t>
+          <t>1764940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>43158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122322</t>
+          <t>124277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>167724</t>
+          <t>168708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151319</t>
+          <t>152198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201429</t>
+          <t>201227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467452</t>
+          <t>466384</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489266</t>
+          <t>489316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>591798</t>
+          <t>590814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>637200</t>
+          <t>635245</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1067635</t>
+          <t>1067837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1117745</t>
+          <t>1116866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139927</t>
+          <t>140672</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>185924</t>
+          <t>187078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149032</t>
+          <t>148287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197740</t>
+          <t>197379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246155</t>
+          <t>247430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260891</t>
+          <t>260428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>923427</t>
+          <t>922273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>969424</t>
+          <t>968679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1178493</t>
+          <t>1178854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1227201</t>
+          <t>1227946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198273</t>
+          <t>197558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>262471</t>
+          <t>262122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>456096</t>
+          <t>455599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>541365</t>
+          <t>540121</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>672140</t>
+          <t>671339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>776028</t>
+          <t>777394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3157448</t>
+          <t>3157797</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3221646</t>
+          <t>3222361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3006760</t>
+          <t>3008004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3092029</t>
+          <t>3092526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6192016</t>
+          <t>6190650</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6295904</t>
+          <t>6296705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>31196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50808</t>
+          <t>49878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402136</t>
+          <t>402073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420182</t>
+          <t>420446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>316849</t>
+          <t>315859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334574</t>
+          <t>334108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725339</t>
+          <t>726269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750005</t>
+          <t>750553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>51444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352888</t>
+          <t>352229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368537</t>
+          <t>368132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341410</t>
+          <t>341396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360554</t>
+          <t>360887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698924</t>
+          <t>698056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725508</t>
+          <t>725124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36244</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>40899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71566</t>
+          <t>72368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477792</t>
+          <t>477765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500045</t>
+          <t>500297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129879</t>
+          <t>130365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150961</t>
+          <t>151092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616470</t>
+          <t>615668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646377</t>
+          <t>647137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79113</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67661</t>
+          <t>66847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101395</t>
+          <t>101729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123866</t>
+          <t>124165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167204</t>
+          <t>168754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1070525</t>
+          <t>1069981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1102217</t>
+          <t>1101159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>724481</t>
+          <t>724147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758215</t>
+          <t>759029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1808310</t>
+          <t>1806760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1851648</t>
+          <t>1851349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60955</t>
+          <t>59665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90847</t>
+          <t>88629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132097</t>
+          <t>129508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132643</t>
+          <t>131234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182469</t>
+          <t>177351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>559751</t>
+          <t>561041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>586310</t>
+          <t>586266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>606147</t>
+          <t>608736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>647397</t>
+          <t>649615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1176481</t>
+          <t>1181599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1226307</t>
+          <t>1227716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>19482</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100835</t>
+          <t>101990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145391</t>
+          <t>144824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110454</t>
+          <t>110769</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>154775</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268041</t>
+          <t>267663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281690</t>
+          <t>281746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>936634</t>
+          <t>937201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>981190</t>
+          <t>980035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1213512</t>
+          <t>1214395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1258716</t>
+          <t>1258401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156808</t>
+          <t>156497</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>212982</t>
+          <t>208825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343723</t>
+          <t>342123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>419177</t>
+          <t>417759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>512483</t>
+          <t>515149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>612765</t>
+          <t>613574</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3172740</t>
+          <t>3176897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3228914</t>
+          <t>3229225</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3112419</t>
+          <t>3113837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3187873</t>
+          <t>3189473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6304553</t>
+          <t>6303744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6404835</t>
+          <t>6402169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -8633,67 +8633,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>34894</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25512</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46588</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31411</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22286</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42173</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55440</t>
+          <t>59943</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41862</t>
+          <t>45667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69945</t>
+          <t>75449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -8746,67 +8746,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>481184</t>
+          <t>525568</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469136</t>
+          <t>512663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489789</t>
+          <t>533928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>453517</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>441823</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>462899</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>92,86%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>416056</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>405294</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>425181</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>897239</t>
+          <t>979086</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882734</t>
+          <t>963580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910817</t>
+          <t>993362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41921</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56285</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>441038</t>
+          <t>470451</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432781</t>
+          <t>460994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446061</t>
+          <t>475901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>351717</t>
+          <t>387798</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340659</t>
+          <t>374933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361269</t>
+          <t>396490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>792755</t>
+          <t>858249</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778508</t>
+          <t>844076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803577</t>
+          <t>870012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64029</t>
+          <t>51583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>55081</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>632044</t>
+          <t>434442</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604235</t>
+          <t>420029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655804</t>
+          <t>446206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151205</t>
+          <t>169585</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144882</t>
+          <t>161725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156177</t>
+          <t>175627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>783249</t>
+          <t>604028</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>755682</t>
+          <t>588926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>813461</t>
+          <t>616212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64566</t>
+          <t>71172</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>57023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>87911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>84684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126007</t>
+          <t>140234</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>119981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149285</t>
+          <t>161034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>969046</t>
+          <t>1059469</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>952683</t>
+          <t>1042730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>982569</t>
+          <t>1073618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>916332</t>
+          <t>791830</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>894075</t>
+          <t>776209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946007</t>
+          <t>803627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1885377</t>
+          <t>1851300</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862099</t>
+          <t>1830500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1921755</t>
+          <t>1871553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033612</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033612</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033612</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977772</t>
+          <t>860893</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977772</t>
+          <t>860893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977772</t>
+          <t>860893</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011384</t>
+          <t>1991534</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011384</t>
+          <t>1991534</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011384</t>
+          <t>1991534</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36377</t>
+          <t>38945</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48944</t>
+          <t>52490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>106930</t>
+          <t>113418</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79818</t>
+          <t>98654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129764</t>
+          <t>132527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>143306</t>
+          <t>152363</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116914</t>
+          <t>133187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168211</t>
+          <t>172938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>438669</t>
+          <t>529019</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426102</t>
+          <t>515474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447971</t>
+          <t>539263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>733846</t>
+          <t>716871</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711012</t>
+          <t>697762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>760958</t>
+          <t>731635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1172515</t>
+          <t>1245889</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1147610</t>
+          <t>1225314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1198907</t>
+          <t>1265065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840776</t>
+          <t>830289</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840776</t>
+          <t>830289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840776</t>
+          <t>830289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1315821</t>
+          <t>1398252</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1315821</t>
+          <t>1398252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315821</t>
+          <t>1398252</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>106088</t>
+          <t>114845</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91092</t>
+          <t>99352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>132836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>117073</t>
+          <t>127538</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98567</t>
+          <t>108063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>149859</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229522</t>
+          <t>224535</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215742</t>
+          <t>210635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235767</t>
+          <t>231869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>654335</t>
+          <t>728413</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>636192</t>
+          <t>710422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>669331</t>
+          <t>743906</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>883857</t>
+          <t>952948</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>862950</t>
+          <t>930627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>902363</t>
+          <t>972423</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760423</t>
+          <t>843258</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760423</t>
+          <t>843258</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760423</t>
+          <t>843258</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000930</t>
+          <t>1080486</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000930</t>
+          <t>1080486</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000930</t>
+          <t>1080486</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>183351</t>
+          <t>197789</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138822</t>
+          <t>174348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>213214</t>
+          <t>229249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>352438</t>
+          <t>385477</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292594</t>
+          <t>351064</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>392823</t>
+          <t>420034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>535790</t>
+          <t>583266</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461699</t>
+          <t>540501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>592714</t>
+          <t>628193</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3191503</t>
+          <t>3243485</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3161640</t>
+          <t>3212025</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3236032</t>
+          <t>3266926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3223490</t>
+          <t>3248013</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3183105</t>
+          <t>3213456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3283334</t>
+          <t>3282426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6414992</t>
+          <t>6491498</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6358068</t>
+          <t>6446571</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6489083</t>
+          <t>6534263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374854</t>
+          <t>3441274</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374854</t>
+          <t>3441274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374854</t>
+          <t>3441274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575928</t>
+          <t>3633490</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575928</t>
+          <t>3633490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575928</t>
+          <t>3633490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950782</t>
+          <t>7074764</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950782</t>
+          <t>7074764</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950782</t>
+          <t>7074764</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
